--- a/erp-server/erp-server-wms/src/main/resources/excel/StocktakingTaskFirstQtyTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/StocktakingTaskFirstQtyTemplate.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <r>
       <rPr>
@@ -51,6 +51,9 @@
       </rPr>
       <t>盘点任务单号</t>
     </r>
+  </si>
+  <si>
+    <t>盘点方式</t>
   </si>
   <si>
     <r>
@@ -79,6 +82,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -93,7 +103,23 @@
     </r>
   </si>
   <si>
+    <t>产品名称</t>
+  </si>
+  <si>
+    <t>可用库存</t>
+  </si>
+  <si>
+    <t>冻结库存</t>
+  </si>
+  <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -110,6 +136,12 @@
   <si>
     <t>盘点库存</t>
   </si>
+  <si>
+    <t>差异数量</t>
+  </si>
+  <si>
+    <t>盘点人</t>
+  </si>
 </sst>
 </file>
 
@@ -121,14 +153,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -615,133 +640,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -750,13 +775,13 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1070,33 +1095,48 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:L1"/>
+  <sheetFormatPr defaultColWidth="13" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="13.75" customWidth="1"/>
-    <col min="2" max="2" width="5.875" customWidth="1"/>
-    <col min="3" max="4" width="5.125" customWidth="1"/>
-    <col min="5" max="6" width="9.625" customWidth="1"/>
+    <col min="1" max="16384" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:6">
+    <row r="1" s="1" customFormat="1" spans="1:12">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
